--- a/Entrega 01/Entrega individual Virginia Bravo/Bases wikipedia/Base de datos Wikipedia.xlsx
+++ b/Entrega 01/Entrega individual Virginia Bravo/Bases wikipedia/Base de datos Wikipedia.xlsx
@@ -1,26 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/virginia_bravo_uc_cl/Documents/Universidad/7° semestre/Narración gráfica/Proyecto-Arratia-Bravo-Finkenberger/Entrega 01/Otros documentos/Bases wikipedia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/virginia_bravo_uc_cl/Documents/Universidad/7° semestre/Narración gráfica/Proyecto-Arratia-Bravo-Finkenberger/Entrega 01/Entrega individual Virginia Bravo/Bases wikipedia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EA2596F-869D-44BF-8EFE-C1A23C1FD198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="184" documentId="8_{4EA2596F-869D-44BF-8EFE-C1A23C1FD198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82EF2AEB-C19F-44C5-8F27-911E85E20932}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="base de datos wikipedia" sheetId="1" r:id="rId1"/>
+    <sheet name="wikipedia" sheetId="1" r:id="rId1"/>
+    <sheet name="google trends" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="149">
   <si>
     <t>ID</t>
   </si>
@@ -31,9 +45,6 @@
     <t>Nombre Común</t>
   </si>
   <si>
-    <t>Categoría</t>
-  </si>
-  <si>
     <t>Promedio Diario</t>
   </si>
   <si>
@@ -41,13 +52,442 @@
   </si>
   <si>
     <t>Total Visitas (periodo seis meses)</t>
+  </si>
+  <si>
+    <t>Acanthogonatus hualpen</t>
+  </si>
+  <si>
+    <t>Aegla denticulata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aegla papudo </t>
+  </si>
+  <si>
+    <t>Alsodes laevis</t>
+  </si>
+  <si>
+    <t>Alsodes norae</t>
+  </si>
+  <si>
+    <t>Alsodes vittatus</t>
+  </si>
+  <si>
+    <t>Ambrosiella kuscheli</t>
+  </si>
+  <si>
+    <t>Anaperochernes ambrosianus</t>
+  </si>
+  <si>
+    <t>Aphrastura masafuerae</t>
+  </si>
+  <si>
+    <t>Biomphalaria costata</t>
+  </si>
+  <si>
+    <t>Brachistosternus philippii</t>
+  </si>
+  <si>
+    <t>Callisphyris ficheti</t>
+  </si>
+  <si>
+    <t>Callyntra hibrida</t>
+  </si>
+  <si>
+    <t>Chelanops pugil</t>
+  </si>
+  <si>
+    <t>Chellius piramidalis</t>
+  </si>
+  <si>
+    <t>Chiasognathus jousselini</t>
+  </si>
+  <si>
+    <t>Chilina angusta</t>
+  </si>
+  <si>
+    <t>Cnemalobus pegnai</t>
+  </si>
+  <si>
+    <t>Ectinogonia barrigai</t>
+  </si>
+  <si>
+    <t>Entomochilus wilsoni</t>
+  </si>
+  <si>
+    <t>Euathlus antai</t>
+  </si>
+  <si>
+    <t>Euathlus atacama</t>
+  </si>
+  <si>
+    <t>Euathlus condorito</t>
+  </si>
+  <si>
+    <t>Euathlus parvulus</t>
+  </si>
+  <si>
+    <t>Eulidia yarrellii</t>
+  </si>
+  <si>
+    <t>Geranoaetus polyosoma exsul</t>
+  </si>
+  <si>
+    <t>Heleobia atacamensis</t>
+  </si>
+  <si>
+    <t>Heleobia transitoria</t>
+  </si>
+  <si>
+    <t>Liolaemus confusus</t>
+  </si>
+  <si>
+    <t>Liolaemus curis</t>
+  </si>
+  <si>
+    <t>Liolaemus hermannunezi</t>
+  </si>
+  <si>
+    <t>Liolaemus melaniceps</t>
+  </si>
+  <si>
+    <t>Liolaemus normae</t>
+  </si>
+  <si>
+    <t>Nigroperla costalis</t>
+  </si>
+  <si>
+    <t>Nycterinus penai</t>
+  </si>
+  <si>
+    <t>Omalonyx gayana</t>
+  </si>
+  <si>
+    <t>Orestias gloriae</t>
+  </si>
+  <si>
+    <t>Orestias piacotensis</t>
+  </si>
+  <si>
+    <t>Palmaspis jubae</t>
+  </si>
+  <si>
+    <t>Paraholopterus nahuelbutensis</t>
+  </si>
+  <si>
+    <t>Phymaturus alicahuense</t>
+  </si>
+  <si>
+    <t>Phymaturus vociferator</t>
+  </si>
+  <si>
+    <t>Pichikadi hualpensis</t>
+  </si>
+  <si>
+    <t>Praocis medvedevi</t>
+  </si>
+  <si>
+    <t>Pristidactylus alvaroi</t>
+  </si>
+  <si>
+    <t>Pseudorestias lirimensis</t>
+  </si>
+  <si>
+    <t>Punctum conicum</t>
+  </si>
+  <si>
+    <t>Punctum depressum</t>
+  </si>
+  <si>
+    <t>Rhinoderma rufum</t>
+  </si>
+  <si>
+    <t>Sclerostomulus nitidus</t>
+  </si>
+  <si>
+    <t>Sephanoides fernandensis</t>
+  </si>
+  <si>
+    <t>Sterphus aurifrons</t>
+  </si>
+  <si>
+    <t>Succinea cryptica</t>
+  </si>
+  <si>
+    <t>Succinea cumingi</t>
+  </si>
+  <si>
+    <t>Succinea fernandi</t>
+  </si>
+  <si>
+    <t>Succinea masafuerae</t>
+  </si>
+  <si>
+    <t>Succinea rubicunda</t>
+  </si>
+  <si>
+    <t>Succinea semiglobosa</t>
+  </si>
+  <si>
+    <t>Succinea texta</t>
+  </si>
+  <si>
+    <t>Swiftia comauensis</t>
+  </si>
+  <si>
+    <t>Telmatobius chusmisensis</t>
+  </si>
+  <si>
+    <t>Telmatobius dankoi</t>
+  </si>
+  <si>
+    <t>Telmatobius fronteriensis</t>
+  </si>
+  <si>
+    <t>Telmatobius halli</t>
+  </si>
+  <si>
+    <t>Telmatobius vilamensis</t>
+  </si>
+  <si>
+    <t>Tornatellina aperta</t>
+  </si>
+  <si>
+    <t>Tornatellina bilamellata</t>
+  </si>
+  <si>
+    <t>Tornatellina callosa</t>
+  </si>
+  <si>
+    <t>Tornatellina plicosa</t>
+  </si>
+  <si>
+    <t>Tornatellina reclusiana</t>
+  </si>
+  <si>
+    <t>Araña (genérico)</t>
+  </si>
+  <si>
+    <t>pancora</t>
+  </si>
+  <si>
+    <t>piñacha, pancora, pancora de Papudo</t>
+  </si>
+  <si>
+    <t>sapo de pecho espinoso de Potrero</t>
+  </si>
+  <si>
+    <t>rana de pecho espinoso de Oncol</t>
+  </si>
+  <si>
+    <t>sapo de pecho espinoso de Malleco</t>
+  </si>
+  <si>
+    <t>caracol</t>
+  </si>
+  <si>
+    <t>seudoescorpión</t>
+  </si>
+  <si>
+    <t>rayadito de Más Afuera</t>
+  </si>
+  <si>
+    <t>caracol de agua dulce</t>
+  </si>
+  <si>
+    <t>escorpión de Philippi</t>
+  </si>
+  <si>
+    <t>sierra del Orocoipo</t>
+  </si>
+  <si>
+    <t>cascarudo híbrido o cascarudo del Poqui</t>
+  </si>
+  <si>
+    <t>caracol de concha piramidal</t>
+  </si>
+  <si>
+    <t>cantárida, ciervo volante peludo</t>
+  </si>
+  <si>
+    <t>caracol de Paposo</t>
+  </si>
+  <si>
+    <t>balita de Barriga, bupréstido de Barriga</t>
+  </si>
+  <si>
+    <t>tenebrio de Wilson, teatino de Wilson</t>
+  </si>
+  <si>
+    <t>araña pollito, tarántula</t>
+  </si>
+  <si>
+    <t>tarántula enana, araña pollito</t>
+  </si>
+  <si>
+    <t>picaflor de Arica, estrellita chilena</t>
+  </si>
+  <si>
+    <t>aguilucho de Más Afuera, aguilucho de Juan Fernández, blindado</t>
+  </si>
+  <si>
+    <t>lagartija de Lolol</t>
+  </si>
+  <si>
+    <t>lagarto negro</t>
+  </si>
+  <si>
+    <t>lagartija de Herman Núñez</t>
+  </si>
+  <si>
+    <t>lagartija</t>
+  </si>
+  <si>
+    <t>lagarto leopardo de Norma, lagarto de los cristales</t>
+  </si>
+  <si>
+    <t>tenebrio de Peña, teatino de Peña</t>
+  </si>
+  <si>
+    <t>caracol terrestre Omalonyx</t>
+  </si>
+  <si>
+    <t>pez (genérico)</t>
+  </si>
+  <si>
+    <t>karachi</t>
+  </si>
+  <si>
+    <t>Escama  gigante de palma chilena</t>
+  </si>
+  <si>
+    <t>matuasto de Alicahue</t>
+  </si>
+  <si>
+    <t>matuasto del Laja, matuasto vociferador</t>
+  </si>
+  <si>
+    <t>caracol costilludo de Hualpén</t>
+  </si>
+  <si>
+    <t>lagarto gruñidor de Álvaro</t>
+  </si>
+  <si>
+    <t>caracol terrestre Punctum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ranita </t>
+  </si>
+  <si>
+    <t>borrachito</t>
+  </si>
+  <si>
+    <t>picaflor de Juan Fernández</t>
+  </si>
+  <si>
+    <t>mosco de Juan Fernández, mosco de rostro dorado</t>
+  </si>
+  <si>
+    <t>caracol terrestre Succinea</t>
+  </si>
+  <si>
+    <t>gorgona amarilla-roja</t>
+  </si>
+  <si>
+    <t>sapo</t>
+  </si>
+  <si>
+    <t>sapo de Danko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sapo </t>
+  </si>
+  <si>
+    <t>rana de Vilama</t>
+  </si>
+  <si>
+    <t>caracol terrestre Tornatellina</t>
+  </si>
+  <si>
+    <t>Clase</t>
+  </si>
+  <si>
+    <t>Arachnida</t>
+  </si>
+  <si>
+    <t>Malacostraca</t>
+  </si>
+  <si>
+    <t>Amphibia</t>
+  </si>
+  <si>
+    <t>Gastropoda</t>
+  </si>
+  <si>
+    <t>Aves</t>
+  </si>
+  <si>
+    <t>Insecta</t>
+  </si>
+  <si>
+    <t>Gasotropoda</t>
+  </si>
+  <si>
+    <t>Reptilia</t>
+  </si>
+  <si>
+    <t>Actinopterygii</t>
+  </si>
+  <si>
+    <t>Anthozoa</t>
+  </si>
+  <si>
+    <t>https://pageviews.wmcloud.org/?project=en.wikipedia.org&amp;platform=all-access&amp;agent=user&amp;redirects=0&amp;start=2025-09-25&amp;end=2026-03-25&amp;pages=Acanthogonatus_hualpen</t>
+  </si>
+  <si>
+    <t>Sin datos</t>
+  </si>
+  <si>
+    <t>https://pageviews.wmcloud.org/?project=en.wikipedia.org&amp;platform=all-access&amp;agent=user&amp;redirects=0&amp;start=2025-09-25&amp;end=2026-03-25&amp;pages=Alsodes_laevis</t>
+  </si>
+  <si>
+    <t>https://pageviews.wmcloud.org/?project=en.wikipedia.org&amp;platform=all-access&amp;agent=user&amp;redirects=0&amp;start=2025-09-25&amp;end=2026-03-25&amp;pages=Alsodes_norae</t>
+  </si>
+  <si>
+    <t>https://pageviews.wmcloud.org/?project=en.wikipedia.org&amp;platform=all-access&amp;agent=user&amp;redirects=0&amp;start=2025-09-25&amp;end=2026-03-25&amp;pages=Alsodes_vittatus</t>
+  </si>
+  <si>
+    <t>https://pageviews.wmcloud.org/?project=en.wikipedia.org&amp;platform=all-access&amp;agent=user&amp;redirects=0&amp;start=2025-09-25&amp;end=2026-03-25&amp;pages=Aphrastura_masafuerae</t>
+  </si>
+  <si>
+    <t>Sin sitio web</t>
+  </si>
+  <si>
+    <t>https://pageviews.wmcloud.org/?project=en.wikipedia.org&amp;platform=all-access&amp;agent=user&amp;redirects=0&amp;start=2025-09-25&amp;end=2026-03-25&amp;pages=Eulidia_yarrellii</t>
+  </si>
+  <si>
+    <t>https://pageviews.wmcloud.org/?project=en.wikipedia.org&amp;platform=all-access&amp;agent=user&amp;redirects=0&amp;start=2025-09-25&amp;end=2026-03-25&amp;pages=Phymaturus_vociferator</t>
+  </si>
+  <si>
+    <t>https://pageviews.wmcloud.org/?project=en.wikipedia.org&amp;platform=all-access&amp;agent=user&amp;redirects=0&amp;start=2025-09-25&amp;end=2026-03-25&amp;pages=Pristidactylus_alvaroi</t>
+  </si>
+  <si>
+    <t>https://pageviews.wmcloud.org/?project=en.wikipedia.org&amp;platform=all-access&amp;agent=user&amp;redirects=0&amp;start=2025-09-25&amp;end=2026-03-25&amp;pages=Pseudorestias_lirimensis</t>
+  </si>
+  <si>
+    <t>https://pageviews.wmcloud.org/?project=en.wikipedia.org&amp;platform=all-access&amp;agent=user&amp;redirects=0&amp;start=2025-09-25&amp;end=2026-03-25&amp;pages=Rhinoderma_rufum</t>
+  </si>
+  <si>
+    <t>https://pageviews.wmcloud.org/?project=en.wikipedia.org&amp;platform=all-access&amp;agent=user&amp;redirects=0&amp;start=2025-09-25&amp;end=2026-03-25&amp;pages=Sephanoides_fernandensis</t>
+  </si>
+  <si>
+    <t>https://pageviews.wmcloud.org/?project=en.wikipedia.org&amp;platform=all-access&amp;agent=user&amp;redirects=0&amp;start=2025-09-25&amp;end=2026-03-25&amp;pages=Sterphus_aurifrons</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -60,16 +500,44 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="CG Times (W1)"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -77,21 +545,224 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{89BB7450-1A81-45B0-B874-B6809C9189F6}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -122,17 +793,37 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B98F516A-28D6-4FB9-81F1-2C9D94D3A83A}" name="Tabla1" displayName="Tabla1" ref="A1:G8" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:G8" xr:uid="{B98F516A-28D6-4FB9-81F1-2C9D94D3A83A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B98F516A-28D6-4FB9-81F1-2C9D94D3A83A}" name="Tabla1" displayName="Tabla1" ref="A1:G71" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:G71" xr:uid="{B98F516A-28D6-4FB9-81F1-2C9D94D3A83A}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{69238F2A-162D-43B2-B7D8-3FC81F366EB5}" name="ID"/>
     <tableColumn id="2" xr3:uid="{C4600FDA-7C40-4DD2-9789-0BB1AAB9FD6C}" name="Nombre Científico"/>
-    <tableColumn id="3" xr3:uid="{CE4C8329-49D0-4CC8-9B40-2F4DF03567EA}" name="Nombre Común"/>
-    <tableColumn id="4" xr3:uid="{C391D303-52F3-4C47-B2AC-F3CDB0E0BB7F}" name="Categoría"/>
+    <tableColumn id="3" xr3:uid="{CE4C8329-49D0-4CC8-9B40-2F4DF03567EA}" name="Nombre Común" dataDxfId="3" dataCellStyle="Normal 3"/>
+    <tableColumn id="4" xr3:uid="{F3492727-C5D3-47DB-AF46-5C37ACDF0D69}" name="Clase" dataDxfId="2" dataCellStyle="Normal 3"/>
     <tableColumn id="5" xr3:uid="{12740CEA-0AA5-4754-B7DD-623297E7B35A}" name="Total Visitas (periodo seis meses)"/>
     <tableColumn id="6" xr3:uid="{B4BA12EB-B3A2-402E-B1FA-B15181DC5518}" name="Promedio Diario"/>
     <tableColumn id="7" xr3:uid="{AEDF878D-AD24-4893-80F2-71AEBCDD79B7}" name="URL Fuente"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC424899-A335-4FA2-8F84-9F94794E961E}" name="Tabla13" displayName="Tabla13" ref="A1:G71" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:G71" xr:uid="{CC424899-A335-4FA2-8F84-9F94794E961E}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{7B6ADD57-2AF2-4072-B5D8-1880205CE9A5}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{D16FBD1F-8DF8-4BDE-862D-01F3F795FA54}" name="Nombre Científico"/>
+    <tableColumn id="3" xr3:uid="{56C7319F-7697-4487-A8D3-44167E195F63}" name="Nombre Común"/>
+    <tableColumn id="4" xr3:uid="{4C399304-441A-4F20-9CEC-365CE3512923}" name="Clase" dataDxfId="0" dataCellStyle="Normal 3"/>
+    <tableColumn id="5" xr3:uid="{21FEE130-6481-43AD-B17B-B8C5E9F82053}" name="Total Visitas (periodo seis meses)"/>
+    <tableColumn id="6" xr3:uid="{88E9B6A2-CB3B-437F-900D-AD2A3C66477A}" name="Promedio Diario"/>
+    <tableColumn id="7" xr3:uid="{67241A42-4BE2-4BBC-84BC-0F4CE1700BF5}" name="URL Fuente"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -339,18 +1030,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G71"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="20.26953125" customWidth="1"/>
-    <col min="3" max="3" width="20.6328125" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="2" max="2" width="31.90625" customWidth="1"/>
+    <col min="3" max="4" width="20.6328125" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="20.26953125" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -361,44 +1051,2389 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="1">
+        <v>97</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5">
+        <v>32</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E6">
+        <v>168</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="E7">
+        <v>643</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" t="s">
+        <v>136</v>
+      </c>
+      <c r="F9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="E10">
+        <v>113</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" t="s">
+        <v>141</v>
+      </c>
+      <c r="F11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" t="s">
+        <v>141</v>
+      </c>
+      <c r="F12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E13" t="s">
+        <v>141</v>
+      </c>
+      <c r="F13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E14" t="s">
+        <v>141</v>
+      </c>
+      <c r="F14" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" t="s">
+        <v>136</v>
+      </c>
+      <c r="F15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" t="s">
+        <v>141</v>
+      </c>
+      <c r="F16" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E17" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F18" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" t="s">
+        <v>141</v>
+      </c>
+      <c r="F19" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" t="s">
+        <v>141</v>
+      </c>
+      <c r="F21" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" t="s">
+        <v>141</v>
+      </c>
+      <c r="F22" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E23" t="s">
+        <v>141</v>
+      </c>
+      <c r="F23" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E24" t="s">
+        <v>141</v>
+      </c>
+      <c r="F24" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E25" t="s">
+        <v>141</v>
+      </c>
+      <c r="F25" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E26">
+        <v>215</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="E27" t="s">
+        <v>141</v>
+      </c>
+      <c r="F27" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" t="s">
+        <v>141</v>
+      </c>
+      <c r="F28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" t="s">
+        <v>141</v>
+      </c>
+      <c r="F29" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" t="s">
+        <v>141</v>
+      </c>
+      <c r="F30" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31" t="s">
+        <v>141</v>
+      </c>
+      <c r="F31" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E32" t="s">
+        <v>141</v>
+      </c>
+      <c r="F32" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E33" t="s">
+        <v>141</v>
+      </c>
+      <c r="F33" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="E34" t="s">
+        <v>141</v>
+      </c>
+      <c r="F34" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="10"/>
+      <c r="D35" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E35" t="s">
+        <v>141</v>
+      </c>
+      <c r="F35" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="E36" t="s">
+        <v>141</v>
+      </c>
+      <c r="F36" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="E37" t="s">
+        <v>141</v>
+      </c>
+      <c r="F37" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="E38" t="s">
+        <v>141</v>
+      </c>
+      <c r="F38" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E39" t="s">
+        <v>136</v>
+      </c>
+      <c r="F39" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="E40" t="s">
+        <v>141</v>
+      </c>
+      <c r="F40" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="10"/>
+      <c r="D41" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E41" t="s">
+        <v>141</v>
+      </c>
+      <c r="F41" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E42" t="s">
+        <v>141</v>
+      </c>
+      <c r="F42" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E43">
+        <v>178</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" s="17" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E44" t="s">
+        <v>141</v>
+      </c>
+      <c r="F44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" s="10"/>
+      <c r="D45" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E45" t="s">
+        <v>141</v>
+      </c>
+      <c r="F45" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="E46">
+        <v>157</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" s="17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="E47">
+        <v>5</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47" s="17" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="E48" t="s">
+        <v>141</v>
+      </c>
+      <c r="F48" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="E49" t="s">
+        <v>141</v>
+      </c>
+      <c r="F49" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="E50">
+        <v>297</v>
+      </c>
+      <c r="F50">
+        <v>2</v>
+      </c>
+      <c r="G50" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E51" t="s">
+        <v>136</v>
+      </c>
+      <c r="F51" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="E52">
+        <v>317</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E53">
+        <v>87</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="E54" t="s">
+        <v>141</v>
+      </c>
+      <c r="F54" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="E55" t="s">
+        <v>141</v>
+      </c>
+      <c r="F55" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D65" s="14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{C64EDCD7-E648-4B6F-B381-D60669DC872C}"/>
+    <hyperlink ref="G5" r:id="rId2" xr:uid="{9D9FD61E-95EB-4393-BF28-BF13D1778A22}"/>
+    <hyperlink ref="G6" r:id="rId3" xr:uid="{F610B55B-4151-4050-B192-7872D12D34B0}"/>
+    <hyperlink ref="G7" r:id="rId4" xr:uid="{E3F9EA51-521B-4DAE-9713-6AD9F445AC7F}"/>
+    <hyperlink ref="G10" r:id="rId5" xr:uid="{7FF656D8-A61F-4667-A401-2E6206385EE0}"/>
+    <hyperlink ref="G26" r:id="rId6" xr:uid="{E8A4E134-0086-49B6-8472-7876F8F64F1C}"/>
+    <hyperlink ref="G43" r:id="rId7" xr:uid="{976E7F0C-70B2-4432-BE3C-0970D7A90082}"/>
+    <hyperlink ref="G46" r:id="rId8" xr:uid="{32D2DE3C-B3D5-43E9-8AD6-DE377A726E00}"/>
+    <hyperlink ref="G47" r:id="rId9" xr:uid="{3373E799-271C-478C-93A3-20DCE391E153}"/>
+    <hyperlink ref="G50" r:id="rId10" xr:uid="{19871289-CC85-4E70-A5CD-449DF7D602DB}"/>
+    <hyperlink ref="G52" r:id="rId11" xr:uid="{0F86B4D1-76F0-49FB-AF4F-357C2375E9CC}"/>
+    <hyperlink ref="G53" r:id="rId12" xr:uid="{04365CBC-B450-4244-A3F5-066EA31A4FF8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId13"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA2D2CA6-5397-4066-90EC-ADBD68E43771}">
+  <dimension ref="A1:G71"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="12.5"/>
+  <cols>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="4" width="20.6328125" customWidth="1"/>
+    <col min="5" max="5" width="33.90625" customWidth="1"/>
+    <col min="6" max="6" width="20.26953125" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>124</v>
+      </c>
       <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
+      <c r="C2" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>126</v>
+      </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>126</v>
+      </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="10"/>
+      <c r="D35" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="10"/>
+      <c r="D41" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" s="10"/>
+      <c r="D45" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D65" s="14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>128</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
